--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -592,9 +592,7 @@
       <c r="G5" s="1" t="n">
         <v>98.92</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,4 +1032,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>29454.75</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>428.25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>28844.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>29743</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>28822.25</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>828472</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>716.0700000000001</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>717.8099999999999</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>723.03</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>713.0700000000001</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>46845961</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>63459.93</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1824.45</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>61867.78</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>64210.53</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>61676.94</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1052</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.98</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>100.14</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>99.81999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86452</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00087</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86389</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86517</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>475781</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5599</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>839837</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.39533</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.39375</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.39612</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.39264</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>331721</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98303</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.9787</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98605</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.97846</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>364886</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>68.176</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>67.84099999999999</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>68.91200000000001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>66.202</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>209014</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4330.09</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4328.74</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4353.11</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4270.56</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>207537</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5724</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>249043</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.6091</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00299</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60462</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.61077</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60453</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>418552</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>160.18</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>160.275</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>160.395</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.858</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>308636</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92009</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.91676</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92052</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.91676</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>379424</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.79782</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00156</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.79866</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.79475</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>358311</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>06/08/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -1040,7 +1040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1089,6 +1089,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1122,6 +1167,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>29117</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>-337.75</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>29435</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>29848.25</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>28227.75</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>1064879</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1155,6 +1231,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>707.83</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>-8.24</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>722.98</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>725.66</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>686.37</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>90552219</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1188,6 +1295,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>62116.25</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-1343.68</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>63493.72</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>63850.66</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>60794.57</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>395</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1213,10 +1351,39 @@
       <c r="G5" s="1" t="n">
         <v>99.81999999999999</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="3" t="n"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>99.68000000000001</v>
+      </c>
+      <c r="S5" s="3" t="n">
         <v/>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="T5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
         </is>
@@ -1254,6 +1421,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.8627899999999999</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>-0.00173</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.86452</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.86504</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.86249</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>447958</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1287,6 +1485,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5621</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5629</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5598</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>822382</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1320,6 +1549,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.39486</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>-0.00047</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.39531</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.39693</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.39193</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>343569</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1353,6 +1613,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.98027</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>-0.00276</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.9830100000000001</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.98498</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.97842</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>364498</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1386,6 +1677,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1419,6 +1741,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1452,6 +1805,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>65.36499999999999</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>-2.811</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-4.12</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>68.176</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>68.92</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>64.43300000000001</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>192809</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1869,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4259.69</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-70.40000000000001</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4330.08</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4360.98</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4237.29</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>190601</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1518,6 +1933,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5723</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5718</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>235343</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1551,6 +1997,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.61014</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.60911</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.61388</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.60818</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>415939</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1584,6 +2061,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>160.367</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>160.18</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>160.445</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>160.055</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>292904</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1617,6 +2125,37 @@
           <t>06/08/26</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.92143</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.00134</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.9201</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.9218499999999999</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.91925</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>367392</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1648,6 +2187,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>06/08/26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.79827</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.79782</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.79916</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.7949000000000001</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>344810</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
         </is>
       </c>
     </row>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -1380,9 +1380,7 @@
       <c r="R5" s="1" t="n">
         <v>99.68000000000001</v>
       </c>
-      <c r="S5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="S5" s="3" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2222,4 +2223,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30559.25</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>897.25</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29907</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30612.5</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29907</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>324793</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>744</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>22.66</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>738.1</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>744.76</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>737.38</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>45713777</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>66520.44</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>3060.41</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>64026.81</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>67276.27</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>64026.81</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>99.65000000000001</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>99.54000000000001</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>99.70999999999999</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86402</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00129</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.8633999999999999</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86521</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>383253</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5613</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5604</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>610739</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.39921</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.3992</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.39941</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.39507</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>311133</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.9893</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00366</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98611</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.99054</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.9847900000000001</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>270619</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>69.97499999999999</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>67.86499999999999</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>71.31100000000001</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>67.86499999999999</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>173997</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4309.33</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>98.42</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4215.13</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4368.76</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4215.13</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>174878</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>222803</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.62139</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00321</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.61991</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.62439</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61959</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>389935</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>160.349</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>160.136</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>160.397</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>159.742</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>274230</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92099</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.9221</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92211</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92005</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>327367</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.79474</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00234</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.79952</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.79952</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.79212</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>305487</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>06/15/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -2404,9 +2404,7 @@
       <c r="G5" s="1" t="n">
         <v>99.38</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2280,6 +2280,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2313,6 +2358,37 @@
           <t>15:59 CT</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>30285.75</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>12220</v>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>08:29 CT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2346,6 +2422,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="n">
+        <v>740.62</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>737.2</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>741.8200000000001</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>732.51</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>49081578</v>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2379,6 +2486,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>63094.81</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>-1311.2</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>64444.89</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>64794.75</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>62276.78</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>259</v>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2410,6 +2548,37 @@
           <t>17:39 ET</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>100.79</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>100.92</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2443,6 +2612,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0.86771</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0.86516</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0.86821</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0.86485</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>459023</v>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2476,6 +2676,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0.5651</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0.5606</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>723827</v>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2509,6 +2740,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.41376</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>1.41005</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>1.41466</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1.40944</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>314439</v>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2542,6 +2804,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0.99161</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0.00264</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0.98897</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0.9936</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0.9886</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>291167</v>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2575,6 +2868,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2608,6 +2932,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2641,6 +2996,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>-2.225</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>-3.27</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>67.944</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>69.82899999999999</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>65.09099999999999</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>190853</v>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2674,6 +3060,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>4209.01</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>-49</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>4257.98</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>4329.63</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>4202.27</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>189053</v>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2707,6 +3124,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>252020</v>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2740,6 +3188,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>1.61981</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>-0.00193</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="P15" s="1" t="n">
+        <v>1.62175</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>1.62603</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1.6185</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>382622</v>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2773,6 +3252,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>161.388</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P16" s="1" t="n">
+        <v>160.654</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>161.81</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>160.483</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>356406</v>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2806,6 +3316,37 @@
           <t>06/15/26</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="M17" s="1" t="n">
+        <v>0.92188</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>0.91981</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>0.92327</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>0.91952</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>389916</v>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2837,6 +3378,37 @@
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>06/15/26</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="M18" s="1" t="n">
+        <v>0.8046</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="P18" s="1" t="n">
+        <v>0.7997300000000001</v>
+      </c>
+      <c r="Q18" s="1" t="n">
+        <v>0.80622</v>
+      </c>
+      <c r="R18" s="1" t="n">
+        <v>0.79822</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>347692</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
         </is>
       </c>
     </row>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2231,7 +2232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T18"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2325,6 +2326,51 @@
           <t>Time</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2389,6 +2435,37 @@
           <t>08:29 CT</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="Y2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="Z2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="AB2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="AC2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>12220</v>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2453,6 +2530,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>740.62</v>
+      </c>
+      <c r="Y3" s="1" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="Z3" s="2" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AA3" s="1" t="n">
+        <v>737.2</v>
+      </c>
+      <c r="AB3" s="1" t="n">
+        <v>741.8200000000001</v>
+      </c>
+      <c r="AC3" s="1" t="n">
+        <v>732.51</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>50154500</v>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2517,6 +2625,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>63226.28</v>
+      </c>
+      <c r="Y4" s="1" t="n">
+        <v>131.47</v>
+      </c>
+      <c r="Z4" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AA4" s="1" t="n">
+        <v>63092.62</v>
+      </c>
+      <c r="AB4" s="1" t="n">
+        <v>63434.16</v>
+      </c>
+      <c r="AC4" s="1" t="n">
+        <v>62327.51</v>
+      </c>
+      <c r="AD4" s="3" t="n">
+        <v>253</v>
+      </c>
+      <c r="AE4" s="4" t="inlineStr">
+        <is>
+          <t>06/19/26</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2571,12 +2710,41 @@
       <c r="R5" s="1" t="n">
         <v>100.21</v>
       </c>
-      <c r="S5" s="3" t="n">
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>100.85</v>
+      </c>
+      <c r="Y5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="1" t="n">
+        <v>100.83</v>
+      </c>
+      <c r="AB5" s="1" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="AC5" s="1" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="AD5" s="3" t="n">
         <v/>
       </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>17:39 ET</t>
+      <c r="AE5" s="4" t="inlineStr">
+        <is>
+          <t>06/19/26</t>
         </is>
       </c>
     </row>
@@ -2643,6 +2811,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>0.86678</v>
+      </c>
+      <c r="Y6" s="1" t="n">
+        <v>-0.0009300000000000001</v>
+      </c>
+      <c r="Z6" s="2" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AA6" s="1" t="n">
+        <v>0.8677</v>
+      </c>
+      <c r="AB6" s="1" t="n">
+        <v>0.86824</v>
+      </c>
+      <c r="AC6" s="1" t="n">
+        <v>0.86574</v>
+      </c>
+      <c r="AD6" s="3" t="n">
+        <v>394691</v>
+      </c>
+      <c r="AE6" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2707,6 +2906,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0.5659</v>
+      </c>
+      <c r="Y7" s="1" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="Z7" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AA7" s="1" t="n">
+        <v>0.5643</v>
+      </c>
+      <c r="AB7" s="1" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="AC7" s="1" t="n">
+        <v>0.5639</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>626003</v>
+      </c>
+      <c r="AE7" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2771,6 +3001,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>1.41536</v>
+      </c>
+      <c r="Y8" s="1" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="Z8" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AA8" s="1" t="n">
+        <v>1.41369</v>
+      </c>
+      <c r="AB8" s="1" t="n">
+        <v>1.41833</v>
+      </c>
+      <c r="AC8" s="1" t="n">
+        <v>1.41268</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>251027</v>
+      </c>
+      <c r="AE8" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2835,6 +3096,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>0.99221</v>
+      </c>
+      <c r="Y9" s="1" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="Z9" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA9" s="1" t="n">
+        <v>0.99161</v>
+      </c>
+      <c r="AB9" s="1" t="n">
+        <v>0.99434</v>
+      </c>
+      <c r="AC9" s="1" t="n">
+        <v>0.98951</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>251564</v>
+      </c>
+      <c r="AE9" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2899,6 +3191,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="Y10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AA10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="AB10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="AC10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="AE10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2963,6 +3286,37 @@
           <t>12/19/25</t>
         </is>
       </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="Y11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AA11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="AB11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="AC11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="AE11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3027,6 +3381,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>64.81</v>
+      </c>
+      <c r="Y12" s="1" t="n">
+        <v>-0.911</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="AA12" s="1" t="n">
+        <v>65.72</v>
+      </c>
+      <c r="AB12" s="1" t="n">
+        <v>65.794</v>
+      </c>
+      <c r="AC12" s="1" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>132782</v>
+      </c>
+      <c r="AE12" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3091,6 +3476,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>4155.53</v>
+      </c>
+      <c r="Y13" s="1" t="n">
+        <v>-53.47</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>4209.02</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>4211.6</v>
+      </c>
+      <c r="AC13" s="1" t="n">
+        <v>4122.2</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>129808</v>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3155,6 +3571,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AA14" s="1" t="n">
+        <v>0.5691000000000001</v>
+      </c>
+      <c r="AB14" s="1" t="n">
+        <v>0.5715</v>
+      </c>
+      <c r="AC14" s="1" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>223236</v>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3219,6 +3666,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>1.62361</v>
+      </c>
+      <c r="Y15" s="1" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AA15" s="1" t="n">
+        <v>1.61982</v>
+      </c>
+      <c r="AB15" s="1" t="n">
+        <v>1.62711</v>
+      </c>
+      <c r="AC15" s="1" t="n">
+        <v>1.61623</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>333921</v>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3283,6 +3761,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="X16" s="1" t="n">
+        <v>161.307</v>
+      </c>
+      <c r="Y16" s="1" t="n">
+        <v>-0.081</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA16" s="1" t="n">
+        <v>161.388</v>
+      </c>
+      <c r="AB16" s="1" t="n">
+        <v>161.455</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>160.99</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>273409</v>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3347,6 +3856,37 @@
           <t>06/18/26</t>
         </is>
       </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="X17" s="1" t="n">
+        <v>0.92582</v>
+      </c>
+      <c r="Y17" s="1" t="n">
+        <v>0.00394</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AA17" s="1" t="n">
+        <v>0.92188</v>
+      </c>
+      <c r="AB17" s="1" t="n">
+        <v>0.92646</v>
+      </c>
+      <c r="AC17" s="1" t="n">
+        <v>0.92182</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>303222</v>
+      </c>
+      <c r="AE17" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3409,6 +3949,659 @@
       <c r="T18" s="4" t="inlineStr">
         <is>
           <t>06/18/26</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="X18" s="1" t="n">
+        <v>0.80703</v>
+      </c>
+      <c r="Y18" s="1" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>0.80459</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>0.8091699999999999</v>
+      </c>
+      <c r="AC18" s="1" t="n">
+        <v>0.80426</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>301781</v>
+      </c>
+      <c r="AE18" s="4" t="inlineStr">
+        <is>
+          <t>15:59 CT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12220</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>737.95</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>742.02</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>745.45</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>734.39</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>43000449</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>64422.14</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>1195.86</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>63839.27</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>65582.13</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>63286.14</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>935</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>100.99</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.08</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.76</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86256</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00422</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86959</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86959</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.86229</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>428528</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5678</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>639415</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.41594</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.41625</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.41934</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.41456</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>292899</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.99131</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.0009</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.99457</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.9907899999999999</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>269314</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>65.10299999999999</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>64.77200000000001</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>67.023</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>175407</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4191.59</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>36.06</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4155.07</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4218.41</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4137.06</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>179688</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5701000000000001</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>238992</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.61818</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00543</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.6242</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.62586</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61711</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>374778</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>161.592</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>161.23</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>161.925</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>161.08</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>346802</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92414</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00168</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92601</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92666</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92378</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>341804</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.8086100000000001</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00158</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.80986</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.80986</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.80697</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>327676</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>06/22/26</t>
         </is>
       </c>
     </row>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -2739,9 +2739,7 @@
       <c r="AC5" s="1" t="n">
         <v>100.7</v>
       </c>
-      <c r="AD5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="AD5" s="3" t="n"/>
       <c r="AE5" s="4" t="inlineStr">
         <is>
           <t>06/19/26</t>
@@ -4167,9 +4165,7 @@
       <c r="G5" s="1" t="n">
         <v>100.76</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Week5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4604,4 +4605,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12220</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>724.08</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>713.99</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>724.58</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>705.17</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>44446121</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>60304.05</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>594.25</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>59650.18</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>60767.22</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>58922.52</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>101.37</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.39</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>101.07</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.86154</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00114</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.86252</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.86325</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>385810</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5562</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0024</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5584</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5591</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>635169</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.42108</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.41938</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.42176</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.41755</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>271449</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.9786899999999999</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.97961</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98027</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.97659</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>263221</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>58.294</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>58.928</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>59.431</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>57.465</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>193903</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4016.61</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-55.34</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4072.49</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4085.27</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4002.65</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>173197</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5683</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5711000000000001</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>206172</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.62339</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00746</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.61582</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.6237</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61524</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>338434</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>161.94</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>161.743</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>161.979</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>161.72</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>246592</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92254</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92084</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92355</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92084</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>309331</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.8076</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.00232</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.80901</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.81035</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.8071700000000001</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>300732</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>06/29/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/june.xlsx
+++ b/outputs/june.xlsx
@@ -4786,9 +4786,7 @@
       <c r="G5" s="1" t="n">
         <v>101.07</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
